--- a/data/projects/drum-pilot/REPORT.xlsx
+++ b/data/projects/drum-pilot/REPORT.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>검증완료</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
